--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\開発演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4784EDE1-31CE-4239-B82A-6049E87A0329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7586EC-20DB-4DFE-994D-90AD5D59C72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1899,12 +1899,14 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I10" s="6">
         <v>46276</v>
       </c>
-      <c r="J10" s="6"/>
+      <c r="J10" s="6">
+        <v>46276</v>
+      </c>
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -1930,9 +1932,11 @@
         <v>1</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I11" s="6">
+        <v>46276</v>
+      </c>
       <c r="J11" s="6"/>
       <c r="K11" s="4"/>
     </row>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7586EC-20DB-4DFE-994D-90AD5D59C72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F605A82D-5BF4-4C33-BBB5-5A1E68142503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1932,12 +1932,14 @@
         <v>1</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I11" s="6">
         <v>46276</v>
       </c>
-      <c r="J11" s="6"/>
+      <c r="J11" s="6">
+        <v>46276</v>
+      </c>
       <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -1963,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -1965,10 +1965,14 @@
         <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46276</v>
+      </c>
+      <c r="J12" s="6">
+        <v>46276</v>
+      </c>
       <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -1352,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>58</v>
@@ -1385,7 +1385,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>16</v>
@@ -1443,7 +1443,7 @@
         <v>23</v>
       </c>
       <c r="G6" s="4">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>21</v>
@@ -1472,7 +1472,7 @@
         <v>23</v>
       </c>
       <c r="G7" s="4">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>21</v>
@@ -1530,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>21</v>
@@ -1575,6 +1575,10 @@
       <c r="F11" s="7">
         <f>SUM(F3:F10)</f>
         <v>78</v>
+      </c>
+      <c r="G11" s="7">
+        <f>SUM(G3:G10)</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F605A82D-5BF4-4C33-BBB5-5A1E68142503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AADF357-2D53-49A5-8AFC-24E1F64B5F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1388,10 +1388,14 @@
         <v>0.5</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I4" s="6">
+        <v>46276</v>
+      </c>
+      <c r="J4" s="6">
+        <v>46276</v>
+      </c>
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2002,10 +2006,14 @@
         <v>0.5</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I13" s="6">
+        <v>46276</v>
+      </c>
+      <c r="J13" s="6">
+        <v>46276</v>
+      </c>
       <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2031,10 +2039,14 @@
         <v>2.5</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I14" s="6">
+        <v>46276</v>
+      </c>
+      <c r="J14" s="6">
+        <v>46276</v>
+      </c>
       <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AADF357-2D53-49A5-8AFC-24E1F64B5F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F416D89F-7E8B-465D-99F8-91C9063A2772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,9 +366,6 @@
     <t>D-2</t>
   </si>
   <si>
-    <t>イベント登録・編集・削除API</t>
-  </si>
-  <si>
     <t>POST/PUT/DELETE /api/events(/{id})、管理者権限のみ</t>
   </si>
   <si>
@@ -641,6 +638,10 @@
     <rPh sb="8" eb="11">
       <t>テイギショ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベント登録・編集・削除API</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1317,7 +1318,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>7</v>
@@ -1421,10 +1422,14 @@
         <v>0.5</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I5" s="6">
+        <v>46276</v>
+      </c>
+      <c r="J5" s="6">
+        <v>46276</v>
+      </c>
       <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1450,9 +1455,11 @@
         <v>1.5</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I6" s="6">
+        <v>46276</v>
+      </c>
       <c r="J6" s="6"/>
       <c r="K6" s="4"/>
     </row>
@@ -1813,7 +1820,7 @@
         <v>69</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>54</v>
@@ -2091,10 +2098,14 @@
         <v>1.5</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I16" s="6">
+        <v>46276</v>
+      </c>
+      <c r="J16" s="6">
+        <v>46276</v>
+      </c>
       <c r="K16" s="4"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -2120,10 +2131,14 @@
         <v>1.5</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I17" s="6">
+        <v>46276</v>
+      </c>
+      <c r="J17" s="6">
+        <v>46276</v>
+      </c>
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2168,10 +2183,14 @@
         <v>3</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I19" s="6">
+        <v>46276</v>
+      </c>
+      <c r="J19" s="6">
+        <v>46279</v>
+      </c>
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2182,10 +2201,10 @@
         <v>28</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>108</v>
@@ -2197,24 +2216,28 @@
         <v>5</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I20" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J20" s="6">
+        <v>46279</v>
+      </c>
       <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>108</v>
@@ -2234,16 +2257,16 @@
     </row>
     <row r="22" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>108</v>
@@ -2263,16 +2286,16 @@
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>108</v>
@@ -2292,22 +2315,22 @@
     </row>
     <row r="24" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>108</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G24" s="4">
         <v>3</v>
@@ -2321,22 +2344,22 @@
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G25" s="4">
         <v>4</v>
@@ -2350,22 +2373,22 @@
     </row>
     <row r="26" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="G26" s="4">
         <v>1</v>
@@ -2398,22 +2421,22 @@
     </row>
     <row r="28" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="G28" s="4">
         <v>4</v>
@@ -2427,22 +2450,22 @@
     </row>
     <row r="29" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G29" s="4">
         <v>2</v>
@@ -2456,51 +2479,53 @@
     </row>
     <row r="30" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="G30" s="4">
         <v>5.5</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I30" s="6">
+        <v>46276</v>
+      </c>
       <c r="J30" s="6"/>
       <c r="K30" s="4"/>
     </row>
     <row r="31" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="G31" s="4">
         <v>4</v>
@@ -2514,51 +2539,55 @@
     </row>
     <row r="32" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="G32" s="4">
         <v>4.5</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I32" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J32" s="6">
+        <v>46279</v>
+      </c>
       <c r="K32" s="4"/>
     </row>
     <row r="33" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="G33" s="4">
         <v>2</v>
@@ -2572,30 +2601,32 @@
     </row>
     <row r="34" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C34" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="F34" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G34" s="4">
         <v>1</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I34" s="6">
+        <v>46279</v>
+      </c>
       <c r="J34" s="6"/>
       <c r="K34" s="4"/>
     </row>
@@ -2620,19 +2651,19 @@
     </row>
     <row r="36" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="E36" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>31</v>
@@ -2649,22 +2680,22 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="F37" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G37" s="4">
         <v>2</v>
@@ -2697,22 +2728,22 @@
     </row>
     <row r="39" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="F39" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G39" s="4">
         <v>2.5</v>
@@ -2726,22 +2757,22 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="E40" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G40" s="4">
         <v>2.5</v>
@@ -2755,22 +2786,22 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="F41" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G41" s="4">
         <v>1.5</v>
@@ -2784,22 +2815,22 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="G42" s="4">
         <v>1.5</v>
@@ -2832,19 +2863,19 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C44" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>39</v>
@@ -2861,22 +2892,22 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="F45" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G45" s="4">
         <v>1</v>
@@ -2890,22 +2921,22 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C46" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>196</v>
-      </c>
       <c r="F46" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G46" s="4">
         <v>1</v>
@@ -2919,7 +2950,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="C47" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G47" s="7">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A3:A46)))*G3:G46)</f>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -1486,9 +1486,11 @@
         <v>1.5</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I7" s="6">
+        <v>46276</v>
+      </c>
       <c r="J7" s="6"/>
       <c r="K7" s="4"/>
     </row>
@@ -2249,10 +2251,14 @@
         <v>3</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I21" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J21" s="6">
+        <v>46279</v>
+      </c>
       <c r="K21" s="4"/>
     </row>
     <row r="22" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2500,12 +2506,14 @@
         <v>5.5</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I30" s="6">
         <v>46276</v>
       </c>
-      <c r="J30" s="6"/>
+      <c r="J30" s="6">
+        <v>46279</v>
+      </c>
       <c r="K30" s="4"/>
     </row>
     <row r="31" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2284,10 +2284,14 @@
         <v>2</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I22" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J22" s="6">
+        <v>46279</v>
+      </c>
       <c r="K22" s="4"/>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2539,9 +2543,11 @@
         <v>4</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I31" s="6">
+        <v>46279</v>
+      </c>
       <c r="J31" s="6"/>
       <c r="K31" s="4"/>
     </row>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2317,10 +2317,14 @@
         <v>2</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I23" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J23" s="6">
+        <v>46279</v>
+      </c>
       <c r="K23" s="4"/>
     </row>
     <row r="24" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2543,12 +2547,14 @@
         <v>4</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I31" s="6">
         <v>46279</v>
       </c>
-      <c r="J31" s="6"/>
+      <c r="J31" s="6">
+        <v>46279</v>
+      </c>
       <c r="K31" s="4"/>
     </row>
     <row r="32" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2350,10 +2350,14 @@
         <v>3</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I24" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J24" s="6">
+        <v>46279</v>
+      </c>
       <c r="K24" s="4"/>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2613,10 +2617,14 @@
         <v>2</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I33" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J33" s="6">
+        <v>46279</v>
+      </c>
       <c r="K33" s="4"/>
     </row>
     <row r="34" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2383,10 +2383,14 @@
         <v>4</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I25" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J25" s="6">
+        <v>46279</v>
+      </c>
       <c r="K25" s="4"/>
     </row>
     <row r="26" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2416,10 +2416,14 @@
         <v>1</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I26" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J26" s="6">
+        <v>46279</v>
+      </c>
       <c r="K26" s="4"/>
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2468,10 +2468,14 @@
         <v>4</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I28" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J28" s="6">
+        <v>46279</v>
+      </c>
       <c r="K28" s="4"/>
     </row>
     <row r="29" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2501,10 +2501,14 @@
         <v>2</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I29" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J29" s="6">
+        <v>46279</v>
+      </c>
       <c r="K29" s="4"/>
     </row>
     <row r="30" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2666,12 +2666,14 @@
         <v>1</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I34" s="6">
         <v>46279</v>
       </c>
-      <c r="J34" s="6"/>
+      <c r="J34" s="6">
+        <v>46279</v>
+      </c>
       <c r="K34" s="4"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2718,10 +2718,14 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I36" s="6">
+        <v>46280</v>
+      </c>
+      <c r="J36" s="6">
+        <v>46280</v>
+      </c>
       <c r="K36" s="4"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2751,10 +2751,14 @@
         <v>2</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I37" s="6">
+        <v>46280</v>
+      </c>
+      <c r="J37" s="6">
+        <v>46280</v>
+      </c>
       <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2803,10 +2803,14 @@
         <v>2.5</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I39" s="6">
+        <v>46280</v>
+      </c>
+      <c r="J39" s="6">
+        <v>46280</v>
+      </c>
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2836,10 +2836,14 @@
         <v>2.5</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I40" s="6">
+        <v>46280</v>
+      </c>
+      <c r="J40" s="6">
+        <v>46280</v>
+      </c>
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2869,10 +2869,14 @@
         <v>1.5</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I41" s="6">
+        <v>46280</v>
+      </c>
+      <c r="J41" s="6">
+        <v>46280</v>
+      </c>
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -2902,10 +2902,14 @@
         <v>1.5</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I42" s="6">
+        <v>46280</v>
+      </c>
+      <c r="J42" s="6">
+        <v>46280</v>
+      </c>
       <c r="K42" s="4"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.55000000000000004">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F416D89F-7E8B-465D-99F8-91C9063A2772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53DAC7B-B2F6-46A2-87CE-A2AAE913AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="フェーズ別WBS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="218">
   <si>
     <t>チーム開発演習 大枠WBS（1人用・イベント申込システム）</t>
   </si>
@@ -642,6 +643,80 @@
   </si>
   <si>
     <t>イベント登録・編集・削除API</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>機能追加・最終テスト</t>
+  </si>
+  <si>
+    <t>I-1</t>
+  </si>
+  <si>
+    <t>機能追加</t>
+  </si>
+  <si>
+    <t>ログイン方式変更・会員登録・イベント検索・カード型UI等の追加実装</t>
+  </si>
+  <si>
+    <t>追加機能一式</t>
+  </si>
+  <si>
+    <t>I-2</t>
+  </si>
+  <si>
+    <t>最終テスト・動作確認</t>
+  </si>
+  <si>
+    <t>追加機能を含めた全体の回帰テスト・動作確認</t>
+  </si>
+  <si>
+    <t>動作確認記録</t>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>J</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能追加</t>
+    <rPh sb="0" eb="4">
+      <t>キノウツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動作確認</t>
+    <rPh sb="0" eb="4">
+      <t>ドウサカクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン、会員登録</t>
+    <rPh sb="5" eb="9">
+      <t>カイイントウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最終テスト</t>
+    <rPh sb="0" eb="2">
+      <t>サイシュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1279,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -1455,12 +1530,14 @@
         <v>1.5</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I6" s="6">
         <v>46276</v>
       </c>
-      <c r="J6" s="6"/>
+      <c r="J6" s="6">
+        <v>46279</v>
+      </c>
       <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1486,12 +1563,14 @@
         <v>1.5</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I7" s="6">
         <v>46276</v>
       </c>
-      <c r="J7" s="6"/>
+      <c r="J7" s="6">
+        <v>46279</v>
+      </c>
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1517,10 +1596,14 @@
         <v>0.5</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I8" s="6">
+        <v>46280</v>
+      </c>
+      <c r="J8" s="6">
+        <v>46280</v>
+      </c>
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1546,57 +1629,118 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="I9" s="6">
+        <v>46279</v>
+      </c>
+      <c r="J9" s="6">
+        <v>46280</v>
+      </c>
       <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>213</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="4">
-        <v>3</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0.5</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
       <c r="H10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I10" s="6">
+        <v>46280</v>
+      </c>
       <c r="J10" s="6"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="7" t="s">
+    <row r="11" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="7">
-        <f>SUM(F3:F10)</f>
+      <c r="F14" s="7">
+        <f>SUM(F3:F13)</f>
         <v>78</v>
       </c>
-      <c r="G11" s="7">
-        <f>SUM(G3:G10)</f>
+      <c r="G14" s="7">
+        <f>SUM(G3:G13)</f>
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A3:K10">
+  <conditionalFormatting sqref="A3:K13">
     <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
       <formula>$H3="未着手"</formula>
     </cfRule>
@@ -1610,7 +1754,7 @@
       <formula>$H3="修正中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H10">
+  <conditionalFormatting sqref="H3:H13">
     <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>$H3="未着手"</formula>
     </cfRule>
@@ -1625,7 +1769,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="未着手 / 着手中 / 完了 / 修正中 から選択してください" promptTitle="状態" prompt="リストから選択" sqref="H3:H10" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="未着手 / 着手中 / 完了 / 修正中 から選択してください" promptTitle="状態" prompt="リストから選択" sqref="H3:H13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"未着手,着手中,完了,修正中"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1635,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
@@ -2914,117 +3058,196 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="8" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:11" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="G44" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="I44" s="6">
+        <v>46281</v>
+      </c>
       <c r="J44" s="6"/>
       <c r="K44" s="4"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="G45" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
       <c r="K45" s="4"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8">
+        <v>3</v>
+      </c>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G47" s="4">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G48" s="4">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B49" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C49" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F49" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G49" s="4">
         <v>1</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H49" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="4"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="C47" s="7" t="s">
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="C50" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G47" s="7">
-        <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A3:A46)))*G3:G46)</f>
-        <v>78</v>
+      <c r="G50" s="7">
+        <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A3:A49)))*G3:G49)</f>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53DAC7B-B2F6-46A2-87CE-A2AAE913AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB2A84C-45A3-4AB1-B7B9-797929F5FC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
     <sheet name="フェーズ別WBS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="218">
   <si>
     <t>チーム開発演習 大枠WBS（1人用・イベント申込システム）</t>
   </si>
@@ -1654,12 +1653,14 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="5" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I10" s="6">
         <v>46280</v>
       </c>
-      <c r="J10" s="6"/>
+      <c r="J10" s="6">
+        <v>46281</v>
+      </c>
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1674,8 +1675,12 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="6"/>
+      <c r="H11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="6">
+        <v>46280</v>
+      </c>
       <c r="J11" s="6"/>
       <c r="K11" s="4"/>
     </row>
@@ -3101,7 +3106,7 @@
         <v>16</v>
       </c>
       <c r="I44" s="6">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44" s="4"/>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB2A84C-45A3-4AB1-B7B9-797929F5FC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675D1CF2-6FFB-4794-97C3-8B5E8183A8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="215">
   <si>
     <t>チーム開発演習 大枠WBS（1人用・イベント申込システム）</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>―</t>
-  </si>
-  <si>
-    <t>着手中</t>
   </si>
   <si>
     <t>B</t>
@@ -683,10 +680,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>J</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>機能追加</t>
     <rPh sb="0" eb="4">
       <t>キノウツイカ</t>
@@ -708,13 +701,6 @@
     <t>ログイン、会員登録</t>
     <rPh sb="5" eb="9">
       <t>カイイントウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>最終テスト</t>
-    <rPh sb="0" eb="2">
-      <t>サイシュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1353,7 +1339,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -1392,7 +1378,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>7</v>
@@ -1430,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I3" s="6">
         <v>46275</v>
@@ -1442,16 +1428,16 @@
     </row>
     <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>11</v>
@@ -1463,7 +1449,7 @@
         <v>0.5</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I4" s="6">
         <v>46276</v>
@@ -1475,19 +1461,19 @@
     </row>
     <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="F5" s="4">
         <v>3</v>
@@ -1496,7 +1482,7 @@
         <v>0.5</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I5" s="6">
         <v>46276</v>
@@ -1508,19 +1494,19 @@
     </row>
     <row r="6" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="4">
         <v>23</v>
@@ -1529,7 +1515,7 @@
         <v>1.5</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I6" s="6">
         <v>46276</v>
@@ -1541,19 +1527,19 @@
     </row>
     <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="4">
         <v>23</v>
@@ -1562,7 +1548,7 @@
         <v>1.5</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I7" s="6">
         <v>46276</v>
@@ -1574,19 +1560,19 @@
     </row>
     <row r="8" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -1595,7 +1581,7 @@
         <v>0.5</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I8" s="6">
         <v>46280</v>
@@ -1607,19 +1593,19 @@
     </row>
     <row r="9" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" s="4">
         <v>8</v>
@@ -1628,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I9" s="6">
         <v>46279</v>
@@ -1640,20 +1626,20 @@
     </row>
     <row r="10" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I10" s="6">
         <v>46280</v>
@@ -1665,10 +1651,10 @@
     </row>
     <row r="11" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1676,7 +1662,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I11" s="6">
         <v>46280</v>
@@ -1686,66 +1672,49 @@
     </row>
     <row r="12" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="4">
+        <v>3</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="4" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="4">
-        <v>3</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="7">
-        <f>SUM(F3:F13)</f>
+      <c r="F13" s="7">
+        <f>SUM(F3:F12)</f>
         <v>78</v>
       </c>
-      <c r="G14" s="7">
-        <f>SUM(G3:G13)</f>
+      <c r="G13" s="7">
+        <f>SUM(G3:G12)</f>
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A3:K13">
+  <conditionalFormatting sqref="A3:K12">
     <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
       <formula>$H3="未着手"</formula>
     </cfRule>
@@ -1759,7 +1728,7 @@
       <formula>$H3="修正中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H13">
+  <conditionalFormatting sqref="H3:H12">
     <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>$H3="未着手"</formula>
     </cfRule>
@@ -1774,7 +1743,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="未着手 / 着手中 / 完了 / 修正中 から選択してください" promptTitle="状態" prompt="リストから選択" sqref="H3:H13" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="未着手 / 着手中 / 完了 / 修正中 から選択してください" promptTitle="状態" prompt="リストから選択" sqref="H3:H12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"未着手,着手中,完了,修正中"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1801,27 +1770,27 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>6</v>
@@ -1860,19 +1829,19 @@
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>15</v>
@@ -1881,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I4" s="6">
         <v>46275</v>
@@ -1893,28 +1862,28 @@
     </row>
     <row r="5" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" s="4">
         <v>2</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I5" s="6">
         <v>46275</v>
@@ -1926,28 +1895,28 @@
     </row>
     <row r="6" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="F6" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" s="4">
         <v>2.5</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I6" s="6">
         <v>46275</v>
@@ -1959,28 +1928,28 @@
     </row>
     <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" s="4">
         <v>2</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I7" s="6">
         <v>46276</v>
@@ -1992,28 +1961,28 @@
     </row>
     <row r="8" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="G8" s="4">
         <v>1.5</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I8" s="6">
         <v>46276</v>
@@ -2025,10 +1994,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -2044,19 +2013,19 @@
     </row>
     <row r="10" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>11</v>
@@ -2065,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I10" s="6">
         <v>46276</v>
@@ -2077,28 +2046,28 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G11" s="4">
         <v>1</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I11" s="6">
         <v>46276</v>
@@ -2110,28 +2079,28 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="F12" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="4">
         <v>1</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I12" s="6">
         <v>46276</v>
@@ -2143,28 +2112,28 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G13" s="4">
         <v>0.5</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I13" s="6">
         <v>46276</v>
@@ -2176,28 +2145,28 @@
     </row>
     <row r="14" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="G14" s="4">
         <v>2.5</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I14" s="6">
         <v>46276</v>
@@ -2209,10 +2178,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>23</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -2228,28 +2197,28 @@
     </row>
     <row r="16" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="G16" s="4">
         <v>1.5</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I16" s="6">
         <v>46276</v>
@@ -2261,28 +2230,28 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G17" s="4">
         <v>1.5</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I17" s="6">
         <v>46276</v>
@@ -2294,10 +2263,10 @@
     </row>
     <row r="18" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -2313,28 +2282,28 @@
     </row>
     <row r="19" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="F19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G19" s="4">
         <v>3</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I19" s="6">
         <v>46276</v>
@@ -2346,28 +2315,28 @@
     </row>
     <row r="20" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" s="4">
         <v>5</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I20" s="6">
         <v>46279</v>
@@ -2379,28 +2348,28 @@
     </row>
     <row r="21" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="E21" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G21" s="4">
         <v>3</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I21" s="6">
         <v>46279</v>
@@ -2412,28 +2381,28 @@
     </row>
     <row r="22" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" s="4">
         <v>2</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I22" s="6">
         <v>46279</v>
@@ -2445,28 +2414,28 @@
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G23" s="4">
         <v>2</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I23" s="6">
         <v>46279</v>
@@ -2478,28 +2447,28 @@
     </row>
     <row r="24" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="E24" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G24" s="4">
         <v>3</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I24" s="6">
         <v>46279</v>
@@ -2511,28 +2480,28 @@
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G25" s="4">
         <v>4</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I25" s="6">
         <v>46279</v>
@@ -2544,28 +2513,28 @@
     </row>
     <row r="26" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="G26" s="4">
         <v>1</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I26" s="6">
         <v>46279</v>
@@ -2577,10 +2546,10 @@
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -2596,28 +2565,28 @@
     </row>
     <row r="28" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="G28" s="4">
         <v>4</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I28" s="6">
         <v>46279</v>
@@ -2629,28 +2598,28 @@
     </row>
     <row r="29" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G29" s="4">
         <v>2</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I29" s="6">
         <v>46279</v>
@@ -2662,28 +2631,28 @@
     </row>
     <row r="30" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="G30" s="4">
         <v>5.5</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I30" s="6">
         <v>46276</v>
@@ -2695,28 +2664,28 @@
     </row>
     <row r="31" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>148</v>
       </c>
       <c r="G31" s="4">
         <v>4</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I31" s="6">
         <v>46279</v>
@@ -2728,28 +2697,28 @@
     </row>
     <row r="32" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="G32" s="4">
         <v>4.5</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I32" s="6">
         <v>46279</v>
@@ -2761,28 +2730,28 @@
     </row>
     <row r="33" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="G33" s="4">
         <v>2</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I33" s="6">
         <v>46279</v>
@@ -2794,28 +2763,28 @@
     </row>
     <row r="34" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="F34" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G34" s="4">
         <v>1</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I34" s="6">
         <v>46279</v>
@@ -2827,10 +2796,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -2846,28 +2815,28 @@
     </row>
     <row r="36" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="E36" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G36" s="4">
         <v>1</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I36" s="6">
         <v>46280</v>
@@ -2879,28 +2848,28 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="F37" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G37" s="4">
         <v>2</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I37" s="6">
         <v>46280</v>
@@ -2912,10 +2881,10 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -2931,28 +2900,28 @@
     </row>
     <row r="39" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="F39" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G39" s="4">
         <v>2.5</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I39" s="6">
         <v>46280</v>
@@ -2964,28 +2933,28 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="E40" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G40" s="4">
         <v>2.5</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I40" s="6">
         <v>46280</v>
@@ -2997,28 +2966,28 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="F41" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G41" s="4">
         <v>1.5</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I41" s="6">
         <v>46280</v>
@@ -3030,28 +2999,28 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="G42" s="4">
         <v>1.5</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I42" s="6">
         <v>46280</v>
@@ -3063,10 +3032,10 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>201</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -3082,70 +3051,76 @@
     </row>
     <row r="44" spans="1:11" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C44" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>205</v>
-      </c>
       <c r="F44" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G44" s="4">
         <v>8</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="I44" s="6">
         <v>46280</v>
       </c>
-      <c r="J44" s="6"/>
+      <c r="J44" s="6">
+        <v>46281</v>
+      </c>
       <c r="K44" s="4"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="D45" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="G45" s="4">
         <v>8</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="I45" s="6">
+        <v>46281</v>
+      </c>
+      <c r="J45" s="6">
+        <v>46281</v>
+      </c>
       <c r="K45" s="4"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>43</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>44</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -3161,28 +3136,28 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C47" s="4" t="s">
+      <c r="D47" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="F47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G47" s="4">
         <v>1</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
@@ -3190,28 +3165,28 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C48" s="4" t="s">
+      <c r="D48" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>191</v>
-      </c>
       <c r="F48" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G48" s="4">
         <v>1</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
@@ -3219,28 +3194,28 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="F49" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G49" s="4">
         <v>1</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
@@ -3248,7 +3223,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="C50" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G50" s="7">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A3:A49)))*G3:G49)</f>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -60,17 +61,23 @@
     </font>
     <font>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -122,7 +129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -144,9 +151,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -157,11 +161,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF7043"/>
+          <bgColor rgb="FFFF7043"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF7F7F7F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE066"/>
+          <bgColor rgb="FFFFE066"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBE0D5"/>
+          <bgColor rgb="FFFBE0D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE4E4E4"/>
+          <bgColor rgb="FFE4E4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF7DB"/>
+          <bgColor rgb="FFFFF7DB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="1"/>
@@ -855,10 +957,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="13" t="n">
         <v>46275</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="J3" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K3" s="4" t="n"/>
@@ -900,10 +1002,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K4" s="4" t="n"/>
@@ -945,10 +1047,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K5" s="4" t="n"/>
@@ -990,10 +1092,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K6" s="4" t="n"/>
@@ -1035,10 +1137,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K7" s="4" t="n"/>
@@ -1080,10 +1182,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="13" t="n">
         <v>46280</v>
       </c>
       <c r="K8" s="4" t="n"/>
@@ -1125,10 +1227,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="13" t="n">
         <v>46280</v>
       </c>
       <c r="K9" s="4" t="n"/>
@@ -1158,10 +1260,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="13" t="n">
         <v>46281</v>
       </c>
       <c r="K10" s="4" t="n"/>
@@ -1187,10 +1289,12 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J11" s="9" t="n"/>
+      <c r="J11" s="13" t="n">
+        <v>46282</v>
+      </c>
       <c r="K11" s="4" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1" s="1">
@@ -1227,11 +1331,15 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>46282</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>46282</v>
+      </c>
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
@@ -1434,10 +1542,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="13" t="n">
         <v>46275</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="13" t="n">
         <v>46275</v>
       </c>
       <c r="K4" s="4" t="n"/>
@@ -1481,10 +1589,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="13" t="n">
         <v>46275</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="13" t="n">
         <v>46275</v>
       </c>
       <c r="K5" s="4" t="n"/>
@@ -1528,10 +1636,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="13" t="n">
         <v>46275</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K6" s="4" t="n"/>
@@ -1575,10 +1683,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K7" s="4" t="n"/>
@@ -1622,10 +1730,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K8" s="4" t="n"/>
@@ -1692,10 +1800,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K10" s="4" t="n"/>
@@ -1739,10 +1847,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K11" s="4" t="n"/>
@@ -1786,10 +1894,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="J12" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K12" s="4" t="n"/>
@@ -1833,10 +1941,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K13" s="4" t="n"/>
@@ -1880,10 +1988,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K14" s="4" t="n"/>
@@ -1950,10 +2058,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K16" s="4" t="n"/>
@@ -1997,10 +2105,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="13" t="n">
         <v>46276</v>
       </c>
       <c r="K17" s="4" t="n"/>
@@ -2067,10 +2175,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K19" s="4" t="n"/>
@@ -2114,10 +2222,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K20" s="4" t="n"/>
@@ -2161,10 +2269,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K21" s="4" t="n"/>
@@ -2208,10 +2316,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K22" s="4" t="n"/>
@@ -2255,10 +2363,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="J23" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K23" s="4" t="n"/>
@@ -2302,10 +2410,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J24" s="9" t="n">
+      <c r="J24" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K24" s="4" t="n"/>
@@ -2349,10 +2457,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K25" s="4" t="n"/>
@@ -2396,10 +2504,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="I26" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J26" s="9" t="n">
+      <c r="J26" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K26" s="4" t="n"/>
@@ -2466,10 +2574,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I28" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K28" s="4" t="n"/>
@@ -2513,10 +2621,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J29" s="9" t="n">
+      <c r="J29" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K29" s="4" t="n"/>
@@ -2560,10 +2668,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I30" s="13" t="n">
         <v>46276</v>
       </c>
-      <c r="J30" s="9" t="n">
+      <c r="J30" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K30" s="4" t="n"/>
@@ -2607,10 +2715,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K31" s="4" t="n"/>
@@ -2654,10 +2762,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="I32" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K32" s="4" t="n"/>
@@ -2701,10 +2809,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K33" s="4" t="n"/>
@@ -2748,10 +2856,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I34" s="9" t="n">
+      <c r="I34" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="J34" s="9" t="n">
+      <c r="J34" s="13" t="n">
         <v>46279</v>
       </c>
       <c r="K34" s="4" t="n"/>
@@ -2818,10 +2926,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I36" s="9" t="n">
+      <c r="I36" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J36" s="9" t="n">
+      <c r="J36" s="13" t="n">
         <v>46280</v>
       </c>
       <c r="K36" s="4" t="n"/>
@@ -2865,10 +2973,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I37" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J37" s="13" t="n">
         <v>46280</v>
       </c>
       <c r="K37" s="4" t="n"/>
@@ -2935,10 +3043,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I39" s="9" t="n">
+      <c r="I39" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J39" s="9" t="n">
+      <c r="J39" s="13" t="n">
         <v>46280</v>
       </c>
       <c r="K39" s="4" t="n"/>
@@ -2982,10 +3090,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I40" s="9" t="n">
+      <c r="I40" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J40" s="9" t="n">
+      <c r="J40" s="13" t="n">
         <v>46280</v>
       </c>
       <c r="K40" s="4" t="n"/>
@@ -3029,10 +3137,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I41" s="9" t="n">
+      <c r="I41" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J41" s="9" t="n">
+      <c r="J41" s="13" t="n">
         <v>46280</v>
       </c>
       <c r="K41" s="4" t="n"/>
@@ -3076,10 +3184,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J42" s="9" t="n">
+      <c r="J42" s="13" t="n">
         <v>46280</v>
       </c>
       <c r="K42" s="4" t="n"/>
@@ -3146,10 +3254,10 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I44" s="9" t="n">
+      <c r="I44" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="J44" s="9" t="n">
+      <c r="J44" s="13" t="n">
         <v>46281</v>
       </c>
       <c r="K44" s="4" t="n"/>
@@ -3193,11 +3301,11 @@
           <t>完了</t>
         </is>
       </c>
-      <c r="I45" s="9" t="n">
+      <c r="I45" s="13" t="n">
         <v>46281</v>
       </c>
-      <c r="J45" s="9" t="n">
-        <v>46281</v>
+      <c r="J45" s="13" t="n">
+        <v>46282</v>
       </c>
       <c r="K45" s="4" t="n"/>
     </row>
@@ -3260,11 +3368,15 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>46282</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>46282</v>
+      </c>
       <c r="K47" s="4" t="n"/>
     </row>
     <row r="48">
@@ -3303,11 +3415,15 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="n"/>
-      <c r="J48" s="9" t="n"/>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="n">
+        <v>46282</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>46282</v>
+      </c>
       <c r="K48" s="4" t="n"/>
     </row>
     <row r="49">
@@ -3346,11 +3462,15 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="9" t="n"/>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="n">
+        <v>46282</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>46282</v>
+      </c>
       <c r="K49" s="4" t="n"/>
     </row>
     <row r="50">
@@ -3365,36 +3485,36 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:K46">
-    <cfRule type="expression" priority="5" dxfId="7" stopIfTrue="1">
+  <conditionalFormatting sqref="A3:K49">
+    <cfRule type="expression" priority="1" dxfId="7">
       <formula>$H3="未着手"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="6" stopIfTrue="1">
+    <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H3="着手中"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="5" stopIfTrue="1">
+    <cfRule type="expression" priority="3" dxfId="5">
       <formula>$H3="完了"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="4" dxfId="4">
       <formula>$H3="修正中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H46">
-    <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="1">
+  <conditionalFormatting sqref="H3:H49">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>$H3="未着手"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="6" dxfId="2">
       <formula>$H3="着手中"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="7" dxfId="1">
       <formula>$H3="完了"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="8" dxfId="0">
       <formula>$H3="修正中"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H3:H46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="未着手 / 着手中 / 完了 / 修正中 から選択してください" promptTitle="状態" prompt="リストから選択" type="list">
+    <dataValidation sqref="H3:H49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="未着手 / 着手中 / 完了 / 修正中 から選択してください" promptTitle="状態" prompt="リストから選択" type="list">
       <formula1>"未着手,着手中,完了,修正中"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3409,7 +3529,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8" customWidth="1" style="1" min="1" max="1"/>
     <col width="22" customWidth="1" style="1" min="2" max="2"/>
@@ -3419,1607 +3539,1665 @@
     <col width="12" customWidth="1" style="1" min="6" max="6"/>
     <col width="11" customWidth="1" style="1" min="7" max="7"/>
     <col width="10" customWidth="1" style="1" min="8" max="8"/>
-    <col width="12" customWidth="1" style="1" min="9" max="9"/>
-    <col width="12" customWidth="1" style="1" min="10" max="10"/>
+    <col width="12" customWidth="1" style="1" min="9" max="10"/>
     <col width="30" customWidth="1" style="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="18.5" customHeight="1" s="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>イベント申込システム 追加開発WBS（v2.0設計書ベース・自己管理用）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>WBS No</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>タスク</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>作業内容</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>成果物</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>先行タスク</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>目安工数(h)</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>開始日</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>完了日</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>DB拡張</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="n">
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="n"/>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="90" customHeight="1" s="1">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>J-1</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>DB拡張</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>既存テーブルへの列追加</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>events(organizer_name/image_url/category/extra_question)、applications(ticket_type_id/extra_answer/checked_in_at)を追加。schema.sql更新・本番DBへALTER TABLE適用</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>更新済みschema.sql・DB</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>46283</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>46283</v>
+      </c>
+      <c r="K4" s="12" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1" s="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>J-2</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>DB拡張</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>新規テーブル作成</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>favorites／ticket_types／event_commentsを作成。ER図・インデックス・FKをテーブル定義書_v2.0.md通りに反映</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>更新済みschema.sql・DB</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>J-1</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>46283</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>46283</v>
+      </c>
+      <c r="K5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1" s="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>バックエンド実装（イベント情報の拡張）</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="54" customHeight="1" s="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>L-1</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（イベント情報の拡張）</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>イベント登録・編集の項目拡張</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Event entity・EventUpsertRequest・EventDetailResponse等に主催者名／画像URL／カテゴリ／アンケート文言を追加</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>更新済みAPI-06/07</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>J-1</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>46283</v>
+      </c>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>PR#3作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1" s="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>L-2</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（イベント情報の拡張）</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>定員区分（TicketType）の実装</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>TicketType entity・repository、Event保存時の区分全置換ロジック、EventDetailResponseへの区分一覧追加</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>更新済みAPI-02/06/07</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>J-2</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>46283</v>
+      </c>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>PR#3作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>L-3</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（イベント情報の拡張）</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>EventServiceの拡張分（区分保存等）の正常系・異常系テスト</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>テストコード</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>L-1,L-2</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>46283</v>
+      </c>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト32件成功。PR#3マージ待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1" s="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>バックエンド実装（申込・キャンセルの区分対応）</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="54" customHeight="1" s="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>M-1</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（申込・キャンセルの区分対応）</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>区分単位の定員判定</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>ApplicationServiceの定員超過チェックを区分単位に対応。区分必須・区分存在チェック（E11/E12）</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>更新済みAPI-03</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>L-2</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="13" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="54" customHeight="1" s="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>M-2</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（申込・キャンセルの区分対応）</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>キャンセル待ちの順位計算・繰り上げ</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>waitlistRankの計算、区分単位でのキャンセル待ち繰り上げ対応</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>更新済みAPI-04/05</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>M-1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1" s="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>M-3</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（申込・キャンセルの区分対応）</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>ApplicationServiceの拡張分（区分判定・順位計算）の正常系・異常系テスト</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>テストコード</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>M-1,M-2</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1" s="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>バックエンド実装（お気に入り）</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（お気に入り）</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>お気に入りAPI実装</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Favorite entity/repository/service/controller。API-15〜17（登録・解除・一覧、冪等処理）</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>API-15〜17</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>J-1</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1" s="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>N-2</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（お気に入り）</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>FavoriteServiceの正常系・冪等系テスト</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>テストコード</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1" s="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>バックエンド実装（イベントコメント）</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="54" customHeight="1" s="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>O-1</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（イベントコメント）</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>コメントAPI実装</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>EventComment entity/repository/service/controller。API-20〜22（一覧・投稿・削除、削除権限チェックE10）</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>API-20〜22</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>J-2</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>DB拡張</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>新規テーブル作成</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>favorites／ticket_types／event_commentsを作成。ER図・インデックス・FKをテーブル定義書_v2.0.md通りに反映</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>更新済みschema.sql・DB</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="G18" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>O-2</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（イベントコメント）</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>EventCommentServiceの正常系・異常系（削除権限）テスト</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>テストコード</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>O-1</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1" s="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>バックエンド実装（当日受付）</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>P-1</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（当日受付）</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>受付APIの実装</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>申込者一覧取得・チェックインAPI。API-18〜19（チェックイン可否チェックE8）</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>API-18〜19</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>J-1</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>P-2</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド実装（当日受付）</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>チェックイン可否チェックの正常系・異常系テスト</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>テストコード</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>P-1</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1" s="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1" s="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Q-1</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>カテゴリ絞り込み</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>イベント検索画面にカテゴリ条件を追加（フロント側フィルタ）</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>更新済みevent-search</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>L-1</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>バックエンド実装（イベント情報の拡張）</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n">
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1" s="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Q-2</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>開催カレンダー表示</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>イベント一覧にカレンダー表示への切り替えを追加</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>更新済みevent-list</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>L-1</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1" s="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Q-3</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>イベント詳細の拡張</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>主催者・画像・カテゴリの表示、区分選択UI、アンケート回答欄をイベント詳細に追加</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>更新済みevent-detail</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>L-2,M-1</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1" s="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Q-4</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>お気に入りボタン</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>イベント一覧・詳細にお気に入りボタンを追加</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>更新済みevent-list/event-detail</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1" s="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Q-5</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>コメント欄</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>イベント詳細にコメント投稿・一覧・削除UIを追加</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>更新済みevent-detail</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>O-1</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1" s="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Q-6</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>マイページの拡張</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>キャンセル待ち順位の表示、お気に入りタブを追加</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>更新済みmy-applications</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>M-2,N-1</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1" s="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（管理者向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>R-1</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（管理者向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>イベント登録・編集フォームの拡張</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>主催者名・画像URL・カテゴリ・アンケート文言・区分（複数、追加/削除可能）の入力欄を追加</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>更新済みadmin-event-form</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>L-1,L-2</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>R-2</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>フロントエンド実装（管理者向け画面拡張）</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>当日受付画面（新規）</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>SC-06：申込者一覧表示・チェックインボタン。ルーティング追加</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>新規admin-checkin画面</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>P-1</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>テスト・結合確認</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>S-1</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>テスト・結合確認</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>結合テスト追加</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>新機能（区分申込・お気に入り・コメント・チェックイン）のAPI/DB結合確認</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>テストコード</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Q,R</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>S-2</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>テスト・結合確認</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>STシナリオ更新</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>一般・管理者シナリオに新機能（区分選択・お気に入り・コメント・受付）を反映</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>更新済みSTシナリオ</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>S-1</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>S-3</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>テスト・結合確認</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>バグ修正・再テスト</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>動作確認で見つかった不具合の修正と再テスト</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>バグチケット</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>S-2</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>発表準備</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>L-1</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（イベント情報の拡張）</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>イベント登録・編集の項目拡張</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Event entity・EventUpsertRequest・EventDetailResponse等に主催者名／画像URL／カテゴリ／アンケート文言を追加</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>更新済みAPI-06/07</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>J-1</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="n">
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>T-1</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>発表準備</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>発表資料作成</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>9スライド構成（表紙〜まとめ）で資料作成</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>発表資料</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>L-2</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（イベント情報の拡張）</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>定員区分（TicketType）の実装</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>TicketType entity・repository、Event保存時の区分全置換ロジック、EventDetailResponseへの区分一覧追加</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>更新済みAPI-02/06/07</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>J-2</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>T-2</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>発表準備</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>デモシナリオ・データ準備</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>一般→管理者の一連の操作シナリオ、エラーを起こせるデータを準備</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>デモシナリオ</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>L-3</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（イベント情報の拡張）</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>ユニットテスト</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>EventServiceの拡張分（区分保存等）の正常系・異常系テスト</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>テストコード</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>L-1,L-2</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="n">
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>発表準備</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>リハーサル</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>所要時間計測、最低1回実施</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>リハーサル記録</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>T-1,T-2</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="n"/>
+      <c r="J40" s="12" t="n"/>
+      <c r="K40" s="12" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>発表準備</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>発表・質疑</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>本番の発表・質疑応答</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
+      <c r="K41" s="12" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>発表準備</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>振り返りシート作成</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>技術面・プロジェクト面・AI駆動開発面（教材ID明記）</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>振り返りシート</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>バックエンド実装（申込・キャンセルの区分対応）</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>M-1</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（申込・キャンセルの区分対応）</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>区分単位の定員判定</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>ApplicationServiceの定員超過チェックを区分単位に対応。区分必須・区分存在チェック（E11/E12）</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>更新済みAPI-03</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>L-2</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="13" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>M-2</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（申込・キャンセルの区分対応）</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>キャンセル待ちの順位計算・繰り上げ</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>waitlistRankの計算、区分単位でのキャンセル待ち繰り上げ対応</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>更新済みAPI-04/05</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>M-1</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="13" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>M-3</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（申込・キャンセルの区分対応）</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>ユニットテスト</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>ApplicationServiceの拡張分（区分判定・順位計算）の正常系・異常系テスト</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>テストコード</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>M-1,M-2</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="13" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>バックエンド実装（お気に入り）</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>N-1</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（お気に入り）</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>お気に入りAPI実装</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Favorite entity/repository/service/controller。API-15〜17（登録・解除・一覧、冪等処理）</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>API-15〜17</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>J-1</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="13" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>N-2</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（お気に入り）</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>ユニットテスト</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>FavoriteServiceの正常系・冪等系テスト</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>テストコード</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>N-1</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>バックエンド実装（イベントコメント）</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>O-1</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（イベントコメント）</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>コメントAPI実装</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>EventComment entity/repository/service/controller。API-20〜22（一覧・投稿・削除、削除権限チェックE10）</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>API-20〜22</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>J-2</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>O-2</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（イベントコメント）</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>ユニットテスト</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>EventCommentServiceの正常系・異常系（削除権限）テスト</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>テストコード</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>O-1</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>バックエンド実装（当日受付）</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>P-1</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（当日受付）</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>受付APIの実装</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>申込者一覧取得・チェックインAPI。API-18〜19（チェックイン可否チェックE8）</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>API-18〜19</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>J-1</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>P-2</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>バックエンド実装（当日受付）</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>ユニットテスト</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>チェックイン可否チェックの正常系・異常系テスト</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>テストコード</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>P-1</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Q-1</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>カテゴリ絞り込み</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>イベント検索画面にカテゴリ条件を追加（フロント側フィルタ）</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>更新済みevent-search</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>L-1</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Q-2</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>開催カレンダー表示</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>イベント一覧にカレンダー表示への切り替えを追加</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>更新済みevent-list</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>L-1</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>Q-3</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>イベント詳細の拡張</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>主催者・画像・カテゴリの表示、区分選択UI、アンケート回答欄をイベント詳細に追加</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>更新済みevent-detail</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>L-2,M-1</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Q-4</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>お気に入りボタン</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>イベント一覧・詳細にお気に入りボタンを追加</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>更新済みevent-list/event-detail</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>N-1</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Q-5</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>コメント欄</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>イベント詳細にコメント投稿・一覧・削除UIを追加</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>更新済みevent-detail</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>O-1</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>Q-6</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（一般ユーザー向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>マイページの拡張</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>キャンセル待ち順位の表示、お気に入りタブを追加</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>更新済みmy-applications</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>M-2,N-1</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（管理者向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>R-1</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（管理者向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>イベント登録・編集フォームの拡張</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>主催者名・画像URL・カテゴリ・アンケート文言・区分（複数、追加/削除可能）の入力欄を追加</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>更新済みadmin-event-form</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>L-1,L-2</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>R-2</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>フロントエンド実装（管理者向け画面拡張）</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>当日受付画面（新規）</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>SC-06：申込者一覧表示・チェックインボタン。ルーティング追加</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>新規admin-checkin画面</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>P-1</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>テスト・結合確認</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>S-1</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>テスト・結合確認</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>結合テスト追加</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>新機能（区分申込・お気に入り・コメント・チェックイン）のAPI/DB結合確認</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>テストコード</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>Q,R</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>S-2</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>テスト・結合確認</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>STシナリオ更新</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>一般・管理者シナリオに新機能（区分選択・お気に入り・コメント・受付）を反映</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>更新済みSTシナリオ</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>S-1</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>S-3</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>テスト・結合確認</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>バグ修正・再テスト</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>動作確認で見つかった不具合の修正と再テスト</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>バグチケット</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>S-2</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>発表準備</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>T-1</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>発表準備</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>発表資料作成</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>9スライド構成（表紙〜まとめ）で資料作成</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>発表資料</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>T-2</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>発表準備</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>デモシナリオ・データ準備</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>一般→管理者の一連の操作シナリオ、エラーを起こせるデータを準備</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>デモシナリオ</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="n"/>
-      <c r="J39" s="13" t="n"/>
-      <c r="K39" s="13" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>T-3</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>発表準備</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>リハーサル</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>所要時間計測、最低1回実施</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>リハーサル記録</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>T-1,T-2</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I40" s="13" t="n"/>
-      <c r="J40" s="13" t="n"/>
-      <c r="K40" s="13" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>発表準備</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>発表・質疑</t>
-        </is>
-      </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>本番の発表・質疑応答</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>T-3</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="13" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>T-5</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>発表準備</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>振り返りシート作成</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>技術面・プロジェクト面・AI駆動開発面（教材ID明記）</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>振り返りシート</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="13" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
     </row>
     <row r="43">
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>合計（タスク工数）</t>
         </is>
       </c>
-      <c r="G43">
+      <c r="G43" s="0">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A4:A42)))*G4:G42)</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A3:K42">
+    <cfRule type="expression" priority="1" dxfId="7">
+      <formula>$H3="未着手"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="6">
+      <formula>$H3="着手中"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="5">
+      <formula>$H3="完了"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="4">
+      <formula>$H3="修正中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H42">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>$H3="未着手"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>$H3="着手中"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>$H3="完了"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>$H3="修正中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="H3:H42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"未着手,着手中,完了,修正中"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -3783,16 +3783,18 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>着手中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="I7" s="14" t="n">
         <v>46283</v>
       </c>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>PR#3作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+          <t>PR#3マージ済み（mainに反映済み）</t>
         </is>
       </c>
     </row>
@@ -3832,16 +3834,18 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>着手中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="I8" s="14" t="n">
         <v>46283</v>
       </c>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>PR#3作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+          <t>PR#3マージ済み（mainに反映済み）</t>
         </is>
       </c>
     </row>
@@ -3881,16 +3885,18 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>着手中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="I9" s="14" t="n">
         <v>46283</v>
       </c>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>ユニットテスト32件成功。PR#3マージ待ち</t>
+          <t>PR#3マージ済み（mainに反映済み）</t>
         </is>
       </c>
     </row>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -3959,12 +3959,18 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>PR#4作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="54" customHeight="1" s="1">
       <c r="A12" s="12" t="inlineStr">
@@ -4002,12 +4008,18 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>PR#4作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1" s="1">
       <c r="A13" s="12" t="inlineStr">
@@ -4045,12 +4057,18 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト成功。PR#4マージ待ち</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1" s="1">
       <c r="A14" s="11" t="inlineStr">
@@ -4111,12 +4129,18 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>PR#5作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="36" customHeight="1" s="1">
       <c r="A16" s="12" t="inlineStr">
@@ -4154,12 +4178,18 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト成功。PR#5マージ待ち</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26" customHeight="1" s="1">
       <c r="A17" s="11" t="inlineStr">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -4250,12 +4250,18 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>PR#6作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1" s="1">
       <c r="A19" s="12" t="inlineStr">
@@ -4293,12 +4299,18 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト成功。PR#6マージ待ち</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="26" customHeight="1" s="1">
       <c r="A20" s="11" t="inlineStr">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -129,7 +128,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -165,6 +164,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4331,7 +4333,7 @@
         <v>4</v>
       </c>
       <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
+      <c r="I20" s="15" t="n"/>
       <c r="J20" s="11" t="n"/>
       <c r="K20" s="11" t="n"/>
     </row>
@@ -4371,12 +4373,18 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>PR#7作成・code-review対応済み。mainマージはユーザー承認待ち</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="36" customHeight="1" s="1">
       <c r="A22" s="12" t="inlineStr">
@@ -4414,12 +4422,18 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>ユニットテスト成功。PR#7マージ待ち</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26" customHeight="1" s="1">
       <c r="A23" s="11" t="inlineStr">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -4494,12 +4495,18 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="54" customHeight="1" s="1">
       <c r="A25" s="12" t="inlineStr">
@@ -4537,12 +4544,18 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="54" customHeight="1" s="1">
       <c r="A26" s="12" t="inlineStr">
@@ -4580,12 +4593,18 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="54" customHeight="1" s="1">
       <c r="A27" s="12" t="inlineStr">
@@ -4623,12 +4642,18 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="54" customHeight="1" s="1">
       <c r="A28" s="12" t="inlineStr">
@@ -4666,12 +4691,18 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="54" customHeight="1" s="1">
       <c r="A29" s="12" t="inlineStr">
@@ -4709,12 +4740,18 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="26" customHeight="1" s="1">
       <c r="A30" s="11" t="inlineStr">
@@ -4775,12 +4812,18 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="36" customHeight="1" s="1">
       <c r="A32" s="12" t="inlineStr">
@@ -4818,12 +4861,18 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -4477,7 +4476,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>イベント検索画面にカテゴリ条件を追加（フロント側フィルタ）</t>
+          <t>イベント検索画面にカテゴリ条件を追加（フロント側フィルタ）→ 実装後、既存イベントにカテゴリ登録が1件も無く不要と判断され撤去</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -4495,7 +4494,7 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>着手中</t>
+          <t>完了（撤去）</t>
         </is>
       </c>
       <c r="I24" s="14" t="n">
@@ -4504,7 +4503,7 @@
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+          <t>PR#8で実装後、機能不要と判断し撤去（バックエンドevents.category列・関連DTO/画面も削除、2026-09-24）</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4574,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>主催者・画像・カテゴリの表示、区分選択UI、アンケート回答欄をイベント詳細に追加</t>
+          <t>主催者・画像の表示、区分選択UI、アンケート回答欄をイベント詳細に追加</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -4794,7 +4793,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>主催者名・画像URL・カテゴリ・アンケート文言・区分（複数、追加/削除可能）の入力欄を追加</t>
+          <t>主催者名・画像URL・アンケート文言・区分（複数、追加/削除可能）の入力欄を追加</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -128,7 +129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -167,6 +168,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3530,7 +3534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8" customWidth="1" style="1" min="1" max="1"/>
@@ -5264,13 +5268,138 @@
       <c r="K42" s="12" t="n"/>
     </row>
     <row r="43">
-      <c r="C43" s="0" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>実装調査・as-built設計書作成</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="11" t="n"/>
+      <c r="K43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>U-1</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>実装調査・as-built設計書作成</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>既存実装のリバースエンジニアリング調査</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド（Controller/Service/Repository/Entity/DTO全ファイル）・フロントエンド（全コンポーネント・ルーティング）・DB定義を実際のソースコードから読解。ビルド・自動テスト実行（backend 61件・frontend 2件）、curl実行によるAPI疎通確認（約25パターン）、稼働中DBとschema.sqlの突合を実施</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>確認ログ（会話記録）</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I44" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="J44" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>既存のdocs/design配下の設計書やコメントは参考情報に留め、コード・実行結果から独立に事実を確認する方針で実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>U-2</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>実装調査・as-built設計書作成</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>as-built設計書の作成</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>U-1の調査結果を基に、要件定義書・テーブル定義書（ER図）・API設計書・画面設計書・画面遷移図・実装事実一覧（根拠ファイル対応表）・未確認事項の7点を新規作成</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>docs/01_要件定義書.md〜docs/07_未確認事項.md（7ファイル）</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>U-1</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I45" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="J45" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>既存のM〜R工程（PR#4〜8）とは独立した棚卸しタスク。マージ状況には影響しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>合計（タスク工数）</t>
         </is>
       </c>
-      <c r="G43" s="0">
-        <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A4:A42)))*G4:G42)</f>
+      <c r="G46" s="0">
+        <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A4:A45)))*G4:G45)</f>
         <v/>
       </c>
     </row>

--- a/docs/開発演習_WBS.xlsx
+++ b/docs/開発演習_WBS.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -128,7 +129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -167,6 +168,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3530,7 +3534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8" customWidth="1" style="1" min="1" max="1"/>
@@ -4476,7 +4480,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>イベント検索画面にカテゴリ条件を追加（フロント側フィルタ）</t>
+          <t>イベント検索画面にカテゴリ条件を追加（フロント側フィルタ）→ 実装後、既存イベントにカテゴリ登録が1件も無く不要と判断され撤去</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -4494,12 +4498,18 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="n"/>
+          <t>完了（撤去）</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>PR#8で実装後、機能不要と判断し撤去（バックエンドevents.category列・関連DTO/画面も削除、2026-09-24）</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="54" customHeight="1" s="1">
       <c r="A25" s="12" t="inlineStr">
@@ -4537,12 +4547,18 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="54" customHeight="1" s="1">
       <c r="A26" s="12" t="inlineStr">
@@ -4562,7 +4578,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>主催者・画像・カテゴリの表示、区分選択UI、アンケート回答欄をイベント詳細に追加</t>
+          <t>主催者・画像の表示、区分選択UI、アンケート回答欄をイベント詳細に追加</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -4580,12 +4596,18 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="54" customHeight="1" s="1">
       <c r="A27" s="12" t="inlineStr">
@@ -4623,12 +4645,18 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="54" customHeight="1" s="1">
       <c r="A28" s="12" t="inlineStr">
@@ -4666,12 +4694,18 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="54" customHeight="1" s="1">
       <c r="A29" s="12" t="inlineStr">
@@ -4709,12 +4743,18 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="26" customHeight="1" s="1">
       <c r="A30" s="11" t="inlineStr">
@@ -4757,7 +4797,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>主催者名・画像URL・カテゴリ・アンケート文言・区分（複数、追加/削除可能）の入力欄を追加</t>
+          <t>主催者名・画像URL・アンケート文言・区分（複数、追加/削除可能）の入力欄を追加</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -4775,12 +4815,18 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="36" customHeight="1" s="1">
       <c r="A32" s="12" t="inlineStr">
@@ -4818,12 +4864,18 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="n"/>
+          <t>着手中</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>46289</v>
+      </c>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>PR#8作成・code-review対応済み。PR#4〜7マージ後にmainマージ予定</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -5216,13 +5268,138 @@
       <c r="K42" s="12" t="n"/>
     </row>
     <row r="43">
-      <c r="C43" s="0" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>実装調査・as-built設計書作成</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="11" t="n"/>
+      <c r="K43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>U-1</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>実装調査・as-built設計書作成</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>既存実装のリバースエンジニアリング調査</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>バックエンド（Controller/Service/Repository/Entity/DTO全ファイル）・フロントエンド（全コンポーネント・ルーティング）・DB定義を実際のソースコードから読解。ビルド・自動テスト実行（backend 61件・frontend 2件）、curl実行によるAPI疎通確認（約25パターン）、稼働中DBとschema.sqlの突合を実施</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>確認ログ（会話記録）</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I44" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="J44" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>既存のdocs/design配下の設計書やコメントは参考情報に留め、コード・実行結果から独立に事実を確認する方針で実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>U-2</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>実装調査・as-built設計書作成</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>as-built設計書の作成</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>U-1の調査結果を基に、要件定義書・テーブル定義書（ER図）・API設計書・画面設計書・画面遷移図・実装事実一覧（根拠ファイル対応表）・未確認事項の7点を新規作成</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>docs/01_要件定義書.md〜docs/07_未確認事項.md（7ファイル）</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>U-1</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I45" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="J45" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>既存のM〜R工程（PR#4〜8）とは独立した棚卸しタスク。マージ状況には影響しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>合計（タスク工数）</t>
         </is>
       </c>
-      <c r="G43" s="0">
-        <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A4:A42)))*G4:G42)</f>
+      <c r="G46" s="0">
+        <f>SUMPRODUCT((ISNUMBER(SEARCH("-",A4:A45)))*G4:G45)</f>
         <v/>
       </c>
     </row>
